--- a/CartRules_702.xlsx
+++ b/CartRules_702.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="43">
   <si>
     <t>Product ID</t>
   </si>
@@ -23,6 +23,126 @@
   </si>
   <si>
     <t>Cart Rules</t>
+  </si>
+  <si>
+    <t>2775</t>
+  </si>
+  <si>
+    <t>5493</t>
+  </si>
+  <si>
+    <t>22327</t>
+  </si>
+  <si>
+    <t>9122</t>
+  </si>
+  <si>
+    <t>5646</t>
+  </si>
+  <si>
+    <t>5647</t>
+  </si>
+  <si>
+    <t>24567</t>
+  </si>
+  <si>
+    <t>21088</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>1654</t>
+  </si>
+  <si>
+    <t>5491</t>
+  </si>
+  <si>
+    <t>8688</t>
+  </si>
+  <si>
+    <t>11844</t>
+  </si>
+  <si>
+    <t>8216</t>
+  </si>
+  <si>
+    <t>8927</t>
+  </si>
+  <si>
+    <t>2422</t>
+  </si>
+  <si>
+    <t>8284</t>
+  </si>
+  <si>
+    <t>12647</t>
+  </si>
+  <si>
+    <t>2912</t>
+  </si>
+  <si>
+    <t>11160</t>
+  </si>
+  <si>
+    <t>12463</t>
+  </si>
+  <si>
+    <t>23038</t>
+  </si>
+  <si>
+    <t>972</t>
+  </si>
+  <si>
+    <t>11158</t>
+  </si>
+  <si>
+    <t>8945</t>
+  </si>
+  <si>
+    <t>3598</t>
+  </si>
+  <si>
+    <t>21480</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>2269</t>
+  </si>
+  <si>
+    <t>1414</t>
+  </si>
+  <si>
+    <t>21320</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
 </sst>
 </file>
@@ -380,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -395,289 +515,355 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>137</v>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3">
-        <v>220</v>
-      </c>
-      <c r="B3">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="C3">
-        <v>60</v>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4">
-        <v>389</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>237</v>
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5">
-        <v>955</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>122</v>
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6">
-        <v>1309</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>63</v>
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7">
-        <v>3337</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>154</v>
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8">
-        <v>3478</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8">
-        <v>90</v>
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9">
-        <v>3900</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
-      <c r="C9">
-        <v>56</v>
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10">
-        <v>5584</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>284</v>
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11">
-        <v>7036</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>149</v>
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12">
-        <v>7324</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>71</v>
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13">
-        <v>8285</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13">
-        <v>556</v>
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14">
-        <v>8557</v>
-      </c>
-      <c r="B14">
-        <v>3</v>
-      </c>
-      <c r="C14">
-        <v>236</v>
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15">
-        <v>9069</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <v>144</v>
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16">
-        <v>9186</v>
-      </c>
-      <c r="B16">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="C16">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17">
-        <v>9910</v>
-      </c>
-      <c r="B17">
-        <v>29</v>
-      </c>
-      <c r="C17">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18">
-        <v>10398</v>
-      </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-      <c r="C18">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19">
-        <v>10536</v>
-      </c>
-      <c r="B19">
-        <v>3</v>
-      </c>
-      <c r="C19">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20">
-        <v>10720</v>
-      </c>
-      <c r="B20">
-        <v>80</v>
-      </c>
-      <c r="C20">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21">
-        <v>11150</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22">
-        <v>12538</v>
-      </c>
-      <c r="B22">
-        <v>3</v>
-      </c>
-      <c r="C22">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23">
-        <v>12924</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24">
-        <v>12925</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25">
-        <v>13283</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26">
-        <v>13498</v>
-      </c>
-      <c r="B26">
-        <v>3</v>
-      </c>
-      <c r="C26">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27">
-        <v>20969</v>
-      </c>
-      <c r="B27">
-        <v>3</v>
-      </c>
-      <c r="C27">
-        <v>701</v>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
